--- a/public/formulacion/modulos/descargas/FORMATO_AE_PARTIDAS_2026.xlsx
+++ b/public/formulacion/modulos/descargas/FORMATO_AE_PARTIDAS_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\matriz_poa\public\formulacion\modulos\descargas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0AFC8FF-A47F-49A1-BD1D-5DF6BAE3F340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB76776D-FC63-4123-AC28-0E47AD3C30E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CLASIF_PRESU_REC Y EGRE_2026'!$A$9:$K$2003</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -4610,10 +4610,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4657,6 +4653,74 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4685,72 +4749,8 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -5168,121 +5168,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="72" t="s">
         <v>1247</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="72" t="s">
         <v>1281</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="72" t="s">
         <v>1300</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="72" t="s">
         <v>1398</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="72" t="s">
         <v>1242</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="73" t="s">
         <v>1248</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
     </row>
     <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.2">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="47" t="s">
         <v>1301</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="58" t="s">
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="74" t="s">
         <v>1399</v>
       </c>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="58"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="74"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="74"/>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="35" t="s">
@@ -5300,92 +5300,92 @@
       <c r="E9" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="75" t="s">
         <v>1401</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="75" t="s">
         <v>1400</v>
       </c>
-      <c r="H9" s="37" t="s">
+      <c r="H9" s="75" t="s">
         <v>1402</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="75" t="s">
         <v>1403</v>
       </c>
-      <c r="J9" s="37" t="s">
+      <c r="J9" s="75" t="s">
         <v>1404</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="75" t="s">
         <v>1405</v>
       </c>
-      <c r="N9" s="51"/>
+      <c r="N9" s="50"/>
     </row>
     <row r="10" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="44" t="s">
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="44">
         <f t="shared" ref="F10:K10" si="0">+F11+F566+F733+F909+F1090+F1247+F1251+F1459+F1545+F1631+F1873+F1980+F1999</f>
         <v>0</v>
       </c>
-      <c r="G10" s="45">
+      <c r="G10" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="45">
+      <c r="H10" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="45">
+      <c r="I10" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="45">
+      <c r="J10" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="45">
+      <c r="K10" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="40" t="s">
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="40">
         <f t="shared" ref="F11:K11" si="1">+F12+F56+F71+F158+F249+F282+F355+F530+F543+F546+F551+F554+F557+F560+F563</f>
         <v>0</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="40">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="40">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="40">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="40">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K11" s="41">
+      <c r="K11" s="40">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -22651,36 +22651,36 @@
       <c r="K565" s="5"/>
     </row>
     <row r="566" spans="1:11" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A566" s="38" t="s">
+      <c r="A566" s="37" t="s">
         <v>247</v>
       </c>
-      <c r="B566" s="39"/>
-      <c r="C566" s="39"/>
-      <c r="D566" s="39"/>
-      <c r="E566" s="40" t="s">
+      <c r="B566" s="38"/>
+      <c r="C566" s="38"/>
+      <c r="D566" s="38"/>
+      <c r="E566" s="39" t="s">
         <v>248</v>
       </c>
-      <c r="F566" s="41">
+      <c r="F566" s="40">
         <f>+F567+F578+F595+F604+F613+F630+F651+F662+F683+F690+F719+F730</f>
         <v>0</v>
       </c>
-      <c r="G566" s="41">
+      <c r="G566" s="40">
         <f t="shared" ref="G566:K566" si="271">+G567+G578+G595+G604+G613+G630+G651+G662+G683+G690+G719+G730</f>
         <v>0</v>
       </c>
-      <c r="H566" s="41">
+      <c r="H566" s="40">
         <f t="shared" si="271"/>
         <v>0</v>
       </c>
-      <c r="I566" s="41">
+      <c r="I566" s="40">
         <f t="shared" si="271"/>
         <v>0</v>
       </c>
-      <c r="J566" s="41">
+      <c r="J566" s="40">
         <f t="shared" si="271"/>
         <v>0</v>
       </c>
-      <c r="K566" s="41">
+      <c r="K566" s="40">
         <f t="shared" si="271"/>
         <v>0</v>
       </c>
@@ -27904,36 +27904,36 @@
       <c r="K732" s="5"/>
     </row>
     <row r="733" spans="1:11" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A733" s="38" t="s">
+      <c r="A733" s="37" t="s">
         <v>337</v>
       </c>
-      <c r="B733" s="39"/>
-      <c r="C733" s="39"/>
-      <c r="D733" s="39"/>
-      <c r="E733" s="40" t="s">
+      <c r="B733" s="38"/>
+      <c r="C733" s="38"/>
+      <c r="D733" s="38"/>
+      <c r="E733" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="F733" s="41">
+      <c r="F733" s="40">
         <f>+F734+F741+F756+F765+F781+F794+F805+F814+F821+F828+F853+F870+F875+F878+F881+F890+F893+F896+F903+F906</f>
         <v>0</v>
       </c>
-      <c r="G733" s="41">
+      <c r="G733" s="40">
         <f t="shared" ref="G733:K733" si="360">+G734+G741+G756+G765+G781+G794+G805+G814+G821+G828+G853+G870+G875+G878+G881+G890+G893+G896+G903+G906</f>
         <v>0</v>
       </c>
-      <c r="H733" s="41">
+      <c r="H733" s="40">
         <f t="shared" si="360"/>
         <v>0</v>
       </c>
-      <c r="I733" s="41">
+      <c r="I733" s="40">
         <f t="shared" si="360"/>
         <v>0</v>
       </c>
-      <c r="J733" s="41">
+      <c r="J733" s="40">
         <f t="shared" si="360"/>
         <v>0</v>
       </c>
-      <c r="K733" s="41">
+      <c r="K733" s="40">
         <f t="shared" si="360"/>
         <v>0</v>
       </c>
@@ -33476,36 +33476,36 @@
       <c r="K908" s="5"/>
     </row>
     <row r="909" spans="1:11" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A909" s="38" t="s">
+      <c r="A909" s="37" t="s">
         <v>432</v>
       </c>
-      <c r="B909" s="39"/>
-      <c r="C909" s="39"/>
-      <c r="D909" s="39"/>
-      <c r="E909" s="40" t="s">
+      <c r="B909" s="38"/>
+      <c r="C909" s="38"/>
+      <c r="D909" s="38"/>
+      <c r="E909" s="39" t="s">
         <v>433</v>
       </c>
-      <c r="F909" s="41">
+      <c r="F909" s="40">
         <f>+F910+F929+F934+F953+F968+F979+F984+F999+F1006+F1015+F1018+F1036+F1049+F1054+F1059+F1076+F1087</f>
         <v>0</v>
       </c>
-      <c r="G909" s="41">
+      <c r="G909" s="40">
         <f t="shared" ref="G909:K909" si="451">+G910+G929+G934+G953+G968+G979+G984+G999+G1006+G1015+G1018+G1036+G1049+G1054+G1059+G1076+G1087</f>
         <v>0</v>
       </c>
-      <c r="H909" s="41">
+      <c r="H909" s="40">
         <f t="shared" si="451"/>
         <v>0</v>
       </c>
-      <c r="I909" s="41">
+      <c r="I909" s="40">
         <f t="shared" si="451"/>
         <v>0</v>
       </c>
-      <c r="J909" s="41">
+      <c r="J909" s="40">
         <f t="shared" si="451"/>
         <v>0</v>
       </c>
-      <c r="K909" s="41">
+      <c r="K909" s="40">
         <f t="shared" si="451"/>
         <v>0</v>
       </c>
@@ -39025,36 +39025,36 @@
       <c r="K1089" s="5"/>
     </row>
     <row r="1090" spans="1:11" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1090" s="38" t="s">
+      <c r="A1090" s="37" t="s">
         <v>536</v>
       </c>
-      <c r="B1090" s="39"/>
-      <c r="C1090" s="39"/>
-      <c r="D1090" s="39"/>
-      <c r="E1090" s="40" t="s">
+      <c r="B1090" s="38"/>
+      <c r="C1090" s="38"/>
+      <c r="D1090" s="38"/>
+      <c r="E1090" s="39" t="s">
         <v>537</v>
       </c>
-      <c r="F1090" s="41">
+      <c r="F1090" s="40">
         <f t="shared" ref="F1090:K1090" si="538">+F1091+F1105+F1114+F1131+F1148+F1157+F1169+F1174+F1181+F1186+F1199+F1210+F1220+F1227+F1230+F1233+F1237+F1244</f>
         <v>0</v>
       </c>
-      <c r="G1090" s="41">
+      <c r="G1090" s="40">
         <f t="shared" si="538"/>
         <v>0</v>
       </c>
-      <c r="H1090" s="41">
+      <c r="H1090" s="40">
         <f t="shared" si="538"/>
         <v>0</v>
       </c>
-      <c r="I1090" s="41">
+      <c r="I1090" s="40">
         <f t="shared" si="538"/>
         <v>0</v>
       </c>
-      <c r="J1090" s="41">
+      <c r="J1090" s="40">
         <f t="shared" si="538"/>
         <v>0</v>
       </c>
-      <c r="K1090" s="41">
+      <c r="K1090" s="40">
         <f t="shared" si="538"/>
         <v>0</v>
       </c>
@@ -43668,36 +43668,36 @@
       <c r="K1246" s="5"/>
     </row>
     <row r="1247" spans="1:11" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1247" s="38" t="s">
+      <c r="A1247" s="37" t="s">
         <v>636</v>
       </c>
-      <c r="B1247" s="39"/>
-      <c r="C1247" s="39"/>
-      <c r="D1247" s="39"/>
-      <c r="E1247" s="40" t="s">
+      <c r="B1247" s="38"/>
+      <c r="C1247" s="38"/>
+      <c r="D1247" s="38"/>
+      <c r="E1247" s="39" t="s">
         <v>637</v>
       </c>
-      <c r="F1247" s="41">
+      <c r="F1247" s="40">
         <f>+F1248</f>
         <v>0</v>
       </c>
-      <c r="G1247" s="41">
+      <c r="G1247" s="40">
         <f t="shared" ref="G1247:K1247" si="602">+G1248</f>
         <v>0</v>
       </c>
-      <c r="H1247" s="41">
+      <c r="H1247" s="40">
         <f t="shared" si="602"/>
         <v>0</v>
       </c>
-      <c r="I1247" s="41">
+      <c r="I1247" s="40">
         <f t="shared" si="602"/>
         <v>0</v>
       </c>
-      <c r="J1247" s="41">
+      <c r="J1247" s="40">
         <f t="shared" si="602"/>
         <v>0</v>
       </c>
-      <c r="K1247" s="41">
+      <c r="K1247" s="40">
         <f t="shared" si="602"/>
         <v>0</v>
       </c>
@@ -43802,36 +43802,36 @@
       <c r="K1250" s="5"/>
     </row>
     <row r="1251" spans="1:11" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1251" s="38" t="s">
+      <c r="A1251" s="37" t="s">
         <v>638</v>
       </c>
-      <c r="B1251" s="39"/>
-      <c r="C1251" s="39"/>
-      <c r="D1251" s="39"/>
-      <c r="E1251" s="40" t="s">
+      <c r="B1251" s="38"/>
+      <c r="C1251" s="38"/>
+      <c r="D1251" s="38"/>
+      <c r="E1251" s="39" t="s">
         <v>639</v>
       </c>
-      <c r="F1251" s="41">
+      <c r="F1251" s="40">
         <f t="shared" ref="F1251:K1251" si="604">+F1252+F1361+F1372+F1401+F1412+F1418+F1421+F1424+F1435+F1440+F1443+F1452</f>
         <v>0</v>
       </c>
-      <c r="G1251" s="41">
+      <c r="G1251" s="40">
         <f t="shared" si="604"/>
         <v>0</v>
       </c>
-      <c r="H1251" s="41">
+      <c r="H1251" s="40">
         <f t="shared" si="604"/>
         <v>0</v>
       </c>
-      <c r="I1251" s="41">
+      <c r="I1251" s="40">
         <f t="shared" si="604"/>
         <v>0</v>
       </c>
-      <c r="J1251" s="41">
+      <c r="J1251" s="40">
         <f t="shared" si="604"/>
         <v>0</v>
       </c>
-      <c r="K1251" s="41">
+      <c r="K1251" s="40">
         <f t="shared" si="604"/>
         <v>0</v>
       </c>
@@ -49278,36 +49278,36 @@
       <c r="K1458" s="5"/>
     </row>
     <row r="1459" spans="1:11" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1459" s="38" t="s">
+      <c r="A1459" s="37" t="s">
         <v>829</v>
       </c>
-      <c r="B1459" s="39"/>
-      <c r="C1459" s="39"/>
-      <c r="D1459" s="39"/>
-      <c r="E1459" s="40" t="s">
+      <c r="B1459" s="38"/>
+      <c r="C1459" s="38"/>
+      <c r="D1459" s="38"/>
+      <c r="E1459" s="39" t="s">
         <v>830</v>
       </c>
-      <c r="F1459" s="41">
+      <c r="F1459" s="40">
         <f t="shared" ref="F1459:K1459" si="646">+F1460+F1479+F1486+F1493+F1498+F1505+F1524+F1533+F1542</f>
         <v>0</v>
       </c>
-      <c r="G1459" s="41">
+      <c r="G1459" s="40">
         <f t="shared" si="646"/>
         <v>0</v>
       </c>
-      <c r="H1459" s="41">
+      <c r="H1459" s="40">
         <f t="shared" si="646"/>
         <v>0</v>
       </c>
-      <c r="I1459" s="41">
+      <c r="I1459" s="40">
         <f t="shared" si="646"/>
         <v>0</v>
       </c>
-      <c r="J1459" s="41">
+      <c r="J1459" s="40">
         <f t="shared" si="646"/>
         <v>0</v>
       </c>
-      <c r="K1459" s="41">
+      <c r="K1459" s="40">
         <f t="shared" si="646"/>
         <v>0</v>
       </c>
@@ -51858,36 +51858,36 @@
       <c r="K1544" s="5"/>
     </row>
     <row r="1545" spans="1:11" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1545" s="38" t="s">
+      <c r="A1545" s="37" t="s">
         <v>889</v>
       </c>
-      <c r="B1545" s="39"/>
-      <c r="C1545" s="39"/>
-      <c r="D1545" s="39"/>
-      <c r="E1545" s="40" t="s">
+      <c r="B1545" s="38"/>
+      <c r="C1545" s="38"/>
+      <c r="D1545" s="38"/>
+      <c r="E1545" s="39" t="s">
         <v>890</v>
       </c>
-      <c r="F1545" s="41">
+      <c r="F1545" s="40">
         <f>+F1546+F1549+F1552+F1555+F1558+F1561+F1564+F1567+F1570+F1575+F1578+F1581+F1584+F1589+F1592+F1595+F1598+F1601+F1604+F1607+F1610+F1613+F1616+F1619+F1622+F1625+F1628</f>
         <v>0</v>
       </c>
-      <c r="G1545" s="41">
+      <c r="G1545" s="40">
         <f t="shared" ref="G1545:K1545" si="684">+G1546+G1549+G1552+G1555+G1558+G1561+G1564+G1567+G1570+G1575+G1578+G1581+G1584+G1589+G1592+G1595+G1598+G1601+G1604+G1607+G1610+G1613+G1616+G1619+G1622+G1625+G1628</f>
         <v>0</v>
       </c>
-      <c r="H1545" s="41">
+      <c r="H1545" s="40">
         <f t="shared" si="684"/>
         <v>0</v>
       </c>
-      <c r="I1545" s="41">
+      <c r="I1545" s="40">
         <f t="shared" si="684"/>
         <v>0</v>
       </c>
-      <c r="J1545" s="41">
+      <c r="J1545" s="40">
         <f t="shared" si="684"/>
         <v>0</v>
       </c>
-      <c r="K1545" s="41">
+      <c r="K1545" s="40">
         <f t="shared" si="684"/>
         <v>0</v>
       </c>
@@ -54690,36 +54690,36 @@
       <c r="K1630" s="5"/>
     </row>
     <row r="1631" spans="1:11" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1631" s="38" t="s">
+      <c r="A1631" s="37" t="s">
         <v>924</v>
       </c>
-      <c r="B1631" s="39"/>
-      <c r="C1631" s="39"/>
-      <c r="D1631" s="39"/>
-      <c r="E1631" s="40" t="s">
+      <c r="B1631" s="38"/>
+      <c r="C1631" s="38"/>
+      <c r="D1631" s="38"/>
+      <c r="E1631" s="39" t="s">
         <v>925</v>
       </c>
-      <c r="F1631" s="41">
+      <c r="F1631" s="40">
         <f t="shared" ref="F1631:K1631" si="716">+F1632+F1691+F1756+F1800+F1851+F1864</f>
         <v>0</v>
       </c>
-      <c r="G1631" s="41">
+      <c r="G1631" s="40">
         <f t="shared" si="716"/>
         <v>0</v>
       </c>
-      <c r="H1631" s="41">
+      <c r="H1631" s="40">
         <f t="shared" si="716"/>
         <v>0</v>
       </c>
-      <c r="I1631" s="41">
+      <c r="I1631" s="40">
         <f t="shared" si="716"/>
         <v>0</v>
       </c>
-      <c r="J1631" s="41">
+      <c r="J1631" s="40">
         <f t="shared" si="716"/>
         <v>0</v>
       </c>
-      <c r="K1631" s="41">
+      <c r="K1631" s="40">
         <f t="shared" si="716"/>
         <v>0</v>
       </c>
@@ -60720,36 +60720,36 @@
       <c r="K1872" s="5"/>
     </row>
     <row r="1873" spans="1:11" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1873" s="38" t="s">
+      <c r="A1873" s="37" t="s">
         <v>1150</v>
       </c>
-      <c r="B1873" s="39"/>
-      <c r="C1873" s="39"/>
-      <c r="D1873" s="39"/>
-      <c r="E1873" s="40" t="s">
+      <c r="B1873" s="38"/>
+      <c r="C1873" s="38"/>
+      <c r="D1873" s="38"/>
+      <c r="E1873" s="39" t="s">
         <v>1151</v>
       </c>
-      <c r="F1873" s="41">
+      <c r="F1873" s="40">
         <f t="shared" ref="F1873:K1873" si="746">+F1874+F1877+F1902+F1911+F1920+F1925+F1932+F1939+F1948+F1955+F1963+F1974+F1977</f>
         <v>0</v>
       </c>
-      <c r="G1873" s="41">
+      <c r="G1873" s="40">
         <f t="shared" si="746"/>
         <v>0</v>
       </c>
-      <c r="H1873" s="41">
+      <c r="H1873" s="40">
         <f t="shared" si="746"/>
         <v>0</v>
       </c>
-      <c r="I1873" s="41">
+      <c r="I1873" s="40">
         <f t="shared" si="746"/>
         <v>0</v>
       </c>
-      <c r="J1873" s="41">
+      <c r="J1873" s="40">
         <f t="shared" si="746"/>
         <v>0</v>
       </c>
-      <c r="K1873" s="41">
+      <c r="K1873" s="40">
         <f t="shared" si="746"/>
         <v>0</v>
       </c>
@@ -64047,36 +64047,36 @@
       <c r="K1979" s="5"/>
     </row>
     <row r="1980" spans="1:11" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1980" s="38" t="s">
+      <c r="A1980" s="37" t="s">
         <v>1215</v>
       </c>
-      <c r="B1980" s="39"/>
-      <c r="C1980" s="39"/>
-      <c r="D1980" s="39"/>
-      <c r="E1980" s="40" t="s">
+      <c r="B1980" s="38"/>
+      <c r="C1980" s="38"/>
+      <c r="D1980" s="38"/>
+      <c r="E1980" s="39" t="s">
         <v>1216</v>
       </c>
-      <c r="F1980" s="41">
+      <c r="F1980" s="40">
         <f>+F1981+F1988+F1991+F1994</f>
         <v>0</v>
       </c>
-      <c r="G1980" s="41">
+      <c r="G1980" s="40">
         <f t="shared" ref="G1980:K1980" si="798">+G1981+G1988+G1991+G1994</f>
         <v>0</v>
       </c>
-      <c r="H1980" s="41">
+      <c r="H1980" s="40">
         <f t="shared" si="798"/>
         <v>0</v>
       </c>
-      <c r="I1980" s="41">
+      <c r="I1980" s="40">
         <f t="shared" si="798"/>
         <v>0</v>
       </c>
-      <c r="J1980" s="41">
+      <c r="J1980" s="40">
         <f t="shared" si="798"/>
         <v>0</v>
       </c>
-      <c r="K1980" s="41">
+      <c r="K1980" s="40">
         <f t="shared" si="798"/>
         <v>0</v>
       </c>
@@ -64664,36 +64664,36 @@
       <c r="K1998" s="5"/>
     </row>
     <row r="1999" spans="1:11" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1999" s="38" t="s">
+      <c r="A1999" s="37" t="s">
         <v>1226</v>
       </c>
-      <c r="B1999" s="39"/>
-      <c r="C1999" s="39"/>
-      <c r="D1999" s="39"/>
-      <c r="E1999" s="40" t="s">
+      <c r="B1999" s="38"/>
+      <c r="C1999" s="38"/>
+      <c r="D1999" s="38"/>
+      <c r="E1999" s="39" t="s">
         <v>1227</v>
       </c>
-      <c r="F1999" s="41">
+      <c r="F1999" s="40">
         <f>+F2000</f>
         <v>0</v>
       </c>
-      <c r="G1999" s="41">
+      <c r="G1999" s="40">
         <f t="shared" ref="G1999:K1999" si="808">+G2000</f>
         <v>0</v>
       </c>
-      <c r="H1999" s="41">
+      <c r="H1999" s="40">
         <f t="shared" si="808"/>
         <v>0</v>
       </c>
-      <c r="I1999" s="41">
+      <c r="I1999" s="40">
         <f t="shared" si="808"/>
         <v>0</v>
       </c>
-      <c r="J1999" s="41">
+      <c r="J1999" s="40">
         <f t="shared" si="808"/>
         <v>0</v>
       </c>
-      <c r="K1999" s="41">
+      <c r="K1999" s="40">
         <f t="shared" si="808"/>
         <v>0</v>
       </c>
@@ -64798,36 +64798,36 @@
       <c r="K2002" s="5"/>
     </row>
     <row r="2003" spans="1:11" s="17" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2003" s="42" t="s">
+      <c r="A2003" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B2003" s="43"/>
-      <c r="C2003" s="43"/>
-      <c r="D2003" s="43"/>
-      <c r="E2003" s="44" t="s">
+      <c r="B2003" s="42"/>
+      <c r="C2003" s="42"/>
+      <c r="D2003" s="42"/>
+      <c r="E2003" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F2003" s="46">
+      <c r="F2003" s="45">
         <f>+F10</f>
         <v>0</v>
       </c>
-      <c r="G2003" s="46">
+      <c r="G2003" s="45">
         <f t="shared" ref="G2003:K2003" si="810">+G10</f>
         <v>0</v>
       </c>
-      <c r="H2003" s="46">
+      <c r="H2003" s="45">
         <f t="shared" si="810"/>
         <v>0</v>
       </c>
-      <c r="I2003" s="46">
+      <c r="I2003" s="45">
         <f t="shared" si="810"/>
         <v>0</v>
       </c>
-      <c r="J2003" s="46">
+      <c r="J2003" s="45">
         <f t="shared" si="810"/>
         <v>0</v>
       </c>
-      <c r="K2003" s="46">
+      <c r="K2003" s="45">
         <f t="shared" si="810"/>
         <v>0</v>
       </c>
@@ -64861,42 +64861,42 @@
       <c r="K2007" s="8"/>
     </row>
     <row r="2008" spans="1:11" ht="24" x14ac:dyDescent="0.2">
-      <c r="A2008" s="52" t="s">
+      <c r="A2008" s="68" t="s">
         <v>1229</v>
       </c>
-      <c r="B2008" s="52"/>
-      <c r="C2008" s="52"/>
-      <c r="D2008" s="52"/>
-      <c r="E2008" s="52"/>
-      <c r="F2008" s="47" t="s">
+      <c r="B2008" s="68"/>
+      <c r="C2008" s="68"/>
+      <c r="D2008" s="68"/>
+      <c r="E2008" s="68"/>
+      <c r="F2008" s="46" t="s">
         <v>1230</v>
       </c>
-      <c r="G2008" s="53" t="s">
+      <c r="G2008" s="69" t="s">
         <v>1231</v>
       </c>
-      <c r="H2008" s="54"/>
-      <c r="I2008" s="54"/>
-      <c r="J2008" s="54"/>
-      <c r="K2008" s="55"/>
+      <c r="H2008" s="70"/>
+      <c r="I2008" s="70"/>
+      <c r="J2008" s="70"/>
+      <c r="K2008" s="71"/>
     </row>
     <row r="2009" spans="1:11" ht="114" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2009" s="59" t="s">
+      <c r="A2009" s="62" t="s">
         <v>1244</v>
       </c>
-      <c r="B2009" s="60"/>
-      <c r="C2009" s="60"/>
-      <c r="D2009" s="60"/>
-      <c r="E2009" s="61"/>
+      <c r="B2009" s="63"/>
+      <c r="C2009" s="63"/>
+      <c r="D2009" s="63"/>
+      <c r="E2009" s="64"/>
       <c r="F2009" s="9" t="s">
         <v>1245</v>
       </c>
-      <c r="G2009" s="62" t="s">
+      <c r="G2009" s="53" t="s">
         <v>1282</v>
       </c>
-      <c r="H2009" s="63"/>
-      <c r="I2009" s="63"/>
-      <c r="J2009" s="63"/>
-      <c r="K2009" s="64"/>
+      <c r="H2009" s="54"/>
+      <c r="I2009" s="54"/>
+      <c r="J2009" s="54"/>
+      <c r="K2009" s="55"/>
     </row>
     <row r="2010" spans="1:11" ht="227.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2010" s="65" t="s">
@@ -64909,89 +64909,89 @@
       <c r="F2010" s="9" t="s">
         <v>1246</v>
       </c>
-      <c r="G2010" s="62" t="s">
+      <c r="G2010" s="53" t="s">
         <v>1282</v>
       </c>
-      <c r="H2010" s="63"/>
-      <c r="I2010" s="63"/>
-      <c r="J2010" s="63"/>
-      <c r="K2010" s="64"/>
+      <c r="H2010" s="54"/>
+      <c r="I2010" s="54"/>
+      <c r="J2010" s="54"/>
+      <c r="K2010" s="55"/>
     </row>
     <row r="2011" spans="1:11" ht="83.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2011" s="68" t="s">
+      <c r="A2011" s="52" t="s">
         <v>1233</v>
       </c>
-      <c r="B2011" s="68"/>
-      <c r="C2011" s="68"/>
-      <c r="D2011" s="68"/>
-      <c r="E2011" s="68"/>
+      <c r="B2011" s="52"/>
+      <c r="C2011" s="52"/>
+      <c r="D2011" s="52"/>
+      <c r="E2011" s="52"/>
       <c r="F2011" s="9" t="s">
         <v>1234</v>
       </c>
-      <c r="G2011" s="62" t="s">
+      <c r="G2011" s="53" t="s">
         <v>1282</v>
       </c>
-      <c r="H2011" s="63"/>
-      <c r="I2011" s="63"/>
-      <c r="J2011" s="63"/>
-      <c r="K2011" s="64"/>
+      <c r="H2011" s="54"/>
+      <c r="I2011" s="54"/>
+      <c r="J2011" s="54"/>
+      <c r="K2011" s="55"/>
     </row>
     <row r="2012" spans="1:11" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2012" s="68" t="s">
+      <c r="A2012" s="52" t="s">
         <v>1235</v>
       </c>
-      <c r="B2012" s="68"/>
-      <c r="C2012" s="68"/>
-      <c r="D2012" s="68"/>
-      <c r="E2012" s="68"/>
+      <c r="B2012" s="52"/>
+      <c r="C2012" s="52"/>
+      <c r="D2012" s="52"/>
+      <c r="E2012" s="52"/>
       <c r="F2012" s="9" t="s">
         <v>1236</v>
       </c>
-      <c r="G2012" s="62" t="s">
+      <c r="G2012" s="53" t="s">
         <v>1282</v>
       </c>
-      <c r="H2012" s="63"/>
-      <c r="I2012" s="63"/>
-      <c r="J2012" s="63"/>
-      <c r="K2012" s="64"/>
+      <c r="H2012" s="54"/>
+      <c r="I2012" s="54"/>
+      <c r="J2012" s="54"/>
+      <c r="K2012" s="55"/>
     </row>
     <row r="2013" spans="1:11" ht="99" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2013" s="70" t="s">
+      <c r="A2013" s="56" t="s">
         <v>1237</v>
       </c>
-      <c r="B2013" s="70"/>
-      <c r="C2013" s="70"/>
-      <c r="D2013" s="70"/>
-      <c r="E2013" s="70"/>
+      <c r="B2013" s="56"/>
+      <c r="C2013" s="56"/>
+      <c r="D2013" s="56"/>
+      <c r="E2013" s="56"/>
       <c r="F2013" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="G2013" s="62" t="s">
+      <c r="G2013" s="53" t="s">
         <v>1282</v>
       </c>
-      <c r="H2013" s="63"/>
-      <c r="I2013" s="63"/>
-      <c r="J2013" s="63"/>
-      <c r="K2013" s="64"/>
+      <c r="H2013" s="54"/>
+      <c r="I2013" s="54"/>
+      <c r="J2013" s="54"/>
+      <c r="K2013" s="55"/>
     </row>
     <row r="2014" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A2014" s="68" t="s">
+      <c r="A2014" s="52" t="s">
         <v>1239</v>
       </c>
-      <c r="B2014" s="68"/>
-      <c r="C2014" s="68"/>
-      <c r="D2014" s="68"/>
-      <c r="E2014" s="68"/>
+      <c r="B2014" s="52"/>
+      <c r="C2014" s="52"/>
+      <c r="D2014" s="52"/>
+      <c r="E2014" s="52"/>
       <c r="F2014" s="10" t="s">
         <v>1240</v>
       </c>
-      <c r="G2014" s="71" t="s">
+      <c r="G2014" s="57" t="s">
         <v>1241</v>
       </c>
-      <c r="H2014" s="72"/>
-      <c r="I2014" s="72"/>
-      <c r="J2014" s="72"/>
-      <c r="K2014" s="73"/>
+      <c r="H2014" s="58"/>
+      <c r="I2014" s="58"/>
+      <c r="J2014" s="58"/>
+      <c r="K2014" s="59"/>
     </row>
     <row r="2015" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2015" s="30"/>
@@ -65022,34 +65022,34 @@
       <c r="K2016" s="8"/>
     </row>
     <row r="2017" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2017" s="74" t="s">
+      <c r="A2017" s="60" t="s">
         <v>1303</v>
       </c>
-      <c r="B2017" s="75"/>
-      <c r="C2017" s="75"/>
-      <c r="D2017" s="75"/>
-      <c r="E2017" s="75"/>
-      <c r="F2017" s="75"/>
-      <c r="G2017" s="75"/>
-      <c r="H2017" s="75"/>
-      <c r="I2017" s="75"/>
-      <c r="J2017" s="75"/>
+      <c r="B2017" s="61"/>
+      <c r="C2017" s="61"/>
+      <c r="D2017" s="61"/>
+      <c r="E2017" s="61"/>
+      <c r="F2017" s="61"/>
+      <c r="G2017" s="61"/>
+      <c r="H2017" s="61"/>
+      <c r="I2017" s="61"/>
+      <c r="J2017" s="61"/>
       <c r="K2017" s="18"/>
     </row>
     <row r="2018" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2018" s="69" t="s">
+      <c r="A2018" s="51" t="s">
         <v>1302</v>
       </c>
-      <c r="B2018" s="69"/>
-      <c r="C2018" s="69"/>
-      <c r="D2018" s="69"/>
-      <c r="E2018" s="69"/>
-      <c r="F2018" s="69"/>
-      <c r="G2018" s="69"/>
-      <c r="H2018" s="69"/>
-      <c r="I2018" s="69"/>
-      <c r="J2018" s="69"/>
-      <c r="K2018" s="69"/>
+      <c r="B2018" s="51"/>
+      <c r="C2018" s="51"/>
+      <c r="D2018" s="51"/>
+      <c r="E2018" s="51"/>
+      <c r="F2018" s="51"/>
+      <c r="G2018" s="51"/>
+      <c r="H2018" s="51"/>
+      <c r="I2018" s="51"/>
+      <c r="J2018" s="51"/>
+      <c r="K2018" s="51"/>
     </row>
   </sheetData>
   <autoFilter ref="A9:K2003" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -65060,20 +65060,6 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="23">
-    <mergeCell ref="A2018:K2018"/>
-    <mergeCell ref="A2012:E2012"/>
-    <mergeCell ref="G2012:K2012"/>
-    <mergeCell ref="A2013:E2013"/>
-    <mergeCell ref="G2013:K2013"/>
-    <mergeCell ref="A2014:E2014"/>
-    <mergeCell ref="G2014:K2014"/>
-    <mergeCell ref="A2017:J2017"/>
-    <mergeCell ref="A2009:E2009"/>
-    <mergeCell ref="G2009:K2009"/>
-    <mergeCell ref="A2010:E2010"/>
-    <mergeCell ref="G2010:K2010"/>
-    <mergeCell ref="A2011:E2011"/>
-    <mergeCell ref="G2011:K2011"/>
     <mergeCell ref="A2008:E2008"/>
     <mergeCell ref="G2008:K2008"/>
     <mergeCell ref="A1:K1"/>
@@ -65083,6 +65069,20 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="F8:K8"/>
+    <mergeCell ref="A2009:E2009"/>
+    <mergeCell ref="G2009:K2009"/>
+    <mergeCell ref="A2010:E2010"/>
+    <mergeCell ref="G2010:K2010"/>
+    <mergeCell ref="A2011:E2011"/>
+    <mergeCell ref="G2011:K2011"/>
+    <mergeCell ref="A2018:K2018"/>
+    <mergeCell ref="A2012:E2012"/>
+    <mergeCell ref="G2012:K2012"/>
+    <mergeCell ref="A2013:E2013"/>
+    <mergeCell ref="G2013:K2013"/>
+    <mergeCell ref="A2014:E2014"/>
+    <mergeCell ref="G2014:K2014"/>
+    <mergeCell ref="A2017:J2017"/>
   </mergeCells>
   <dataValidations disablePrompts="1" xWindow="44" yWindow="229" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="::: NO MODIFICAR :::" prompt="Total de la Partida 4 EGRESOS" sqref="B2003:C2003 B10:C10" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
